--- a/고반식당_서비스MOT체크리스트_v4_1.xlsx
+++ b/고반식당_서비스MOT체크리스트_v4_1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pc\Documents\00_GOBAN\___MOT체크리스트\MOT_체크리스트_최종본\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BED5552-8433-4FC6-9055-E8E0C811ADE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA27BABB-41AC-4057-AB03-C845AC11387C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1365,18 +1365,59 @@
     <xf numFmtId="0" fontId="30" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="11" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1390,6 +1431,12 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1403,53 +1450,6 @@
     <xf numFmtId="0" fontId="4" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="28" fillId="19" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1809,63 +1809,63 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="83" t="s">
+      <c r="A1" s="62" t="s">
         <v>127</v>
       </c>
-      <c r="B1" s="84"/>
-      <c r="C1" s="84"/>
-      <c r="D1" s="84"/>
-      <c r="E1" s="84"/>
-      <c r="F1" s="84"/>
-      <c r="G1" s="84"/>
-      <c r="H1" s="84"/>
-      <c r="I1" s="85"/>
+      <c r="B1" s="63"/>
+      <c r="C1" s="63"/>
+      <c r="D1" s="63"/>
+      <c r="E1" s="63"/>
+      <c r="F1" s="63"/>
+      <c r="G1" s="63"/>
+      <c r="H1" s="63"/>
+      <c r="I1" s="64"/>
       <c r="K1" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="80" t="s">
+      <c r="A2" s="59" t="s">
         <v>99</v>
       </c>
-      <c r="B2" s="81"/>
-      <c r="C2" s="81"/>
-      <c r="D2" s="81"/>
-      <c r="E2" s="81"/>
-      <c r="F2" s="81"/>
-      <c r="G2" s="81"/>
-      <c r="H2" s="81"/>
-      <c r="I2" s="82"/>
+      <c r="B2" s="60"/>
+      <c r="C2" s="60"/>
+      <c r="D2" s="60"/>
+      <c r="E2" s="60"/>
+      <c r="F2" s="60"/>
+      <c r="G2" s="60"/>
+      <c r="H2" s="60"/>
+      <c r="I2" s="61"/>
     </row>
     <row r="3" spans="1:11" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="79" t="s">
+      <c r="A3" s="58" t="s">
         <v>100</v>
       </c>
-      <c r="B3" s="79"/>
-      <c r="C3" s="79"/>
-      <c r="D3" s="79"/>
-      <c r="E3" s="79"/>
-      <c r="F3" s="79"/>
-      <c r="G3" s="86" t="s">
+      <c r="B3" s="58"/>
+      <c r="C3" s="58"/>
+      <c r="D3" s="58"/>
+      <c r="E3" s="58"/>
+      <c r="F3" s="58"/>
+      <c r="G3" s="65" t="s">
         <v>131</v>
       </c>
-      <c r="H3" s="87"/>
-      <c r="I3" s="87"/>
+      <c r="H3" s="66"/>
+      <c r="I3" s="66"/>
     </row>
     <row r="4" spans="1:11" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="89" t="s">
+      <c r="A4" s="68" t="s">
         <v>132</v>
       </c>
-      <c r="B4" s="90"/>
-      <c r="C4" s="90"/>
-      <c r="D4" s="90"/>
-      <c r="E4" s="90"/>
-      <c r="F4" s="90"/>
-      <c r="G4" s="86" t="s">
+      <c r="B4" s="69"/>
+      <c r="C4" s="69"/>
+      <c r="D4" s="69"/>
+      <c r="E4" s="69"/>
+      <c r="F4" s="69"/>
+      <c r="G4" s="65" t="s">
         <v>52</v>
       </c>
-      <c r="H4" s="87"/>
-      <c r="I4" s="87"/>
+      <c r="H4" s="66"/>
+      <c r="I4" s="66"/>
     </row>
     <row r="5" spans="1:11" ht="24" x14ac:dyDescent="0.3">
       <c r="A5" s="23" t="s">
@@ -1897,12 +1897,12 @@
       </c>
     </row>
     <row r="6" spans="1:11" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="62" t="s">
+      <c r="A6" s="79" t="s">
         <v>37</v>
       </c>
-      <c r="B6" s="63"/>
-      <c r="C6" s="63"/>
-      <c r="D6" s="63"/>
+      <c r="B6" s="80"/>
+      <c r="C6" s="80"/>
+      <c r="D6" s="80"/>
       <c r="E6" s="19" t="s">
         <v>51</v>
       </c>
@@ -1956,10 +1956,10 @@
       </c>
       <c r="F8" s="7"/>
       <c r="G8" s="7">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="H8" s="7">
-        <v>-2</v>
+        <v>-4</v>
       </c>
       <c r="I8" s="36"/>
     </row>
@@ -1981,10 +1981,10 @@
       </c>
       <c r="F9" s="17"/>
       <c r="G9" s="17">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="H9" s="17">
-        <v>-2</v>
+        <v>-4</v>
       </c>
       <c r="I9" s="35" t="s">
         <v>86</v>
@@ -2008,10 +2008,10 @@
       </c>
       <c r="F10" s="7"/>
       <c r="G10" s="7">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="H10" s="7">
-        <v>-2</v>
+        <v>-4</v>
       </c>
       <c r="I10" s="36" t="s">
         <v>87</v>
@@ -2043,30 +2043,30 @@
       <c r="I11" s="15"/>
     </row>
     <row r="12" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="66" t="s">
+      <c r="A12" s="83" t="s">
         <v>41</v>
       </c>
-      <c r="B12" s="60"/>
-      <c r="C12" s="60"/>
-      <c r="D12" s="60"/>
-      <c r="E12" s="60"/>
-      <c r="F12" s="60"/>
-      <c r="G12" s="60"/>
-      <c r="H12" s="60"/>
-      <c r="I12" s="61"/>
+      <c r="B12" s="73"/>
+      <c r="C12" s="73"/>
+      <c r="D12" s="73"/>
+      <c r="E12" s="73"/>
+      <c r="F12" s="73"/>
+      <c r="G12" s="73"/>
+      <c r="H12" s="73"/>
+      <c r="I12" s="74"/>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A13" s="88" t="s">
+      <c r="A13" s="67" t="s">
         <v>101</v>
       </c>
-      <c r="B13" s="78"/>
-      <c r="C13" s="78"/>
-      <c r="D13" s="78"/>
-      <c r="E13" s="78"/>
-      <c r="F13" s="78"/>
-      <c r="G13" s="78"/>
-      <c r="H13" s="78"/>
-      <c r="I13" s="78"/>
+      <c r="B13" s="57"/>
+      <c r="C13" s="57"/>
+      <c r="D13" s="57"/>
+      <c r="E13" s="57"/>
+      <c r="F13" s="57"/>
+      <c r="G13" s="57"/>
+      <c r="H13" s="57"/>
+      <c r="I13" s="57"/>
     </row>
     <row r="14" spans="1:11" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="27" t="s">
@@ -2144,17 +2144,17 @@
       <c r="I16" s="5"/>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A17" s="77" t="s">
+      <c r="A17" s="56" t="s">
         <v>102</v>
       </c>
-      <c r="B17" s="78"/>
-      <c r="C17" s="78"/>
-      <c r="D17" s="78"/>
-      <c r="E17" s="78"/>
-      <c r="F17" s="78"/>
-      <c r="G17" s="78"/>
-      <c r="H17" s="78"/>
-      <c r="I17" s="78"/>
+      <c r="B17" s="57"/>
+      <c r="C17" s="57"/>
+      <c r="D17" s="57"/>
+      <c r="E17" s="57"/>
+      <c r="F17" s="57"/>
+      <c r="G17" s="57"/>
+      <c r="H17" s="57"/>
+      <c r="I17" s="57"/>
     </row>
     <row r="18" spans="1:9" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="26" t="s">
@@ -2232,17 +2232,17 @@
       <c r="I20" s="43"/>
     </row>
     <row r="21" spans="1:9" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="71" t="s">
+      <c r="A21" s="90" t="s">
         <v>38</v>
       </c>
-      <c r="B21" s="60"/>
-      <c r="C21" s="60"/>
-      <c r="D21" s="60"/>
-      <c r="E21" s="60"/>
-      <c r="F21" s="60"/>
-      <c r="G21" s="60"/>
-      <c r="H21" s="60"/>
-      <c r="I21" s="61"/>
+      <c r="B21" s="73"/>
+      <c r="C21" s="73"/>
+      <c r="D21" s="73"/>
+      <c r="E21" s="73"/>
+      <c r="F21" s="73"/>
+      <c r="G21" s="73"/>
+      <c r="H21" s="73"/>
+      <c r="I21" s="74"/>
     </row>
     <row r="22" spans="1:9" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="16">
@@ -2373,17 +2373,17 @@
       <c r="I26" s="48"/>
     </row>
     <row r="27" spans="1:9" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="59" t="s">
+      <c r="A27" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="B27" s="60"/>
-      <c r="C27" s="60"/>
-      <c r="D27" s="60"/>
-      <c r="E27" s="60"/>
-      <c r="F27" s="60"/>
-      <c r="G27" s="60"/>
-      <c r="H27" s="60"/>
-      <c r="I27" s="61"/>
+      <c r="B27" s="73"/>
+      <c r="C27" s="73"/>
+      <c r="D27" s="73"/>
+      <c r="E27" s="73"/>
+      <c r="F27" s="73"/>
+      <c r="G27" s="73"/>
+      <c r="H27" s="73"/>
+      <c r="I27" s="74"/>
     </row>
     <row r="28" spans="1:9" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="16">
@@ -2619,17 +2619,17 @@
       <c r="I36" s="15"/>
     </row>
     <row r="37" spans="1:9" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="73" t="s">
+      <c r="A37" s="72" t="s">
         <v>42</v>
       </c>
-      <c r="B37" s="60"/>
-      <c r="C37" s="60"/>
-      <c r="D37" s="60"/>
-      <c r="E37" s="60"/>
-      <c r="F37" s="60"/>
-      <c r="G37" s="60"/>
-      <c r="H37" s="60"/>
-      <c r="I37" s="61"/>
+      <c r="B37" s="73"/>
+      <c r="C37" s="73"/>
+      <c r="D37" s="73"/>
+      <c r="E37" s="73"/>
+      <c r="F37" s="73"/>
+      <c r="G37" s="73"/>
+      <c r="H37" s="73"/>
+      <c r="I37" s="74"/>
     </row>
     <row r="38" spans="1:9" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="1">
@@ -2733,17 +2733,17 @@
       <c r="I41" s="5"/>
     </row>
     <row r="42" spans="1:9" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="71" t="s">
+      <c r="A42" s="90" t="s">
         <v>56</v>
       </c>
-      <c r="B42" s="60"/>
-      <c r="C42" s="60"/>
-      <c r="D42" s="60"/>
-      <c r="E42" s="60"/>
-      <c r="F42" s="60"/>
-      <c r="G42" s="60"/>
-      <c r="H42" s="60"/>
-      <c r="I42" s="61"/>
+      <c r="B42" s="73"/>
+      <c r="C42" s="73"/>
+      <c r="D42" s="73"/>
+      <c r="E42" s="73"/>
+      <c r="F42" s="73"/>
+      <c r="G42" s="73"/>
+      <c r="H42" s="73"/>
+      <c r="I42" s="74"/>
     </row>
     <row r="43" spans="1:9" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="1">
@@ -2824,17 +2824,17 @@
       </c>
     </row>
     <row r="46" spans="1:9" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="74" t="s">
+      <c r="A46" s="75" t="s">
         <v>48</v>
       </c>
-      <c r="B46" s="60"/>
-      <c r="C46" s="60"/>
-      <c r="D46" s="60"/>
-      <c r="E46" s="60"/>
-      <c r="F46" s="60"/>
-      <c r="G46" s="60"/>
-      <c r="H46" s="60"/>
-      <c r="I46" s="61"/>
+      <c r="B46" s="73"/>
+      <c r="C46" s="73"/>
+      <c r="D46" s="73"/>
+      <c r="E46" s="73"/>
+      <c r="F46" s="73"/>
+      <c r="G46" s="73"/>
+      <c r="H46" s="73"/>
+      <c r="I46" s="74"/>
     </row>
     <row r="47" spans="1:9" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="6">
@@ -2887,17 +2887,17 @@
       <c r="I48" s="43"/>
     </row>
     <row r="49" spans="1:9" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="68" t="s">
+      <c r="A49" s="87" t="s">
         <v>45</v>
       </c>
-      <c r="B49" s="69"/>
-      <c r="C49" s="69"/>
-      <c r="D49" s="69"/>
-      <c r="E49" s="69"/>
-      <c r="F49" s="69"/>
-      <c r="G49" s="69"/>
-      <c r="H49" s="69"/>
-      <c r="I49" s="70"/>
+      <c r="B49" s="88"/>
+      <c r="C49" s="88"/>
+      <c r="D49" s="88"/>
+      <c r="E49" s="88"/>
+      <c r="F49" s="88"/>
+      <c r="G49" s="88"/>
+      <c r="H49" s="88"/>
+      <c r="I49" s="89"/>
     </row>
     <row r="50" spans="1:9" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="11">
@@ -3004,104 +3004,90 @@
       <c r="I53" s="5"/>
     </row>
     <row r="54" spans="1:9" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="75" t="s">
+      <c r="A54" s="76" t="s">
         <v>24</v>
       </c>
-      <c r="B54" s="76"/>
-      <c r="C54" s="76"/>
-      <c r="D54" s="76"/>
-      <c r="E54" s="76"/>
+      <c r="B54" s="77"/>
+      <c r="C54" s="77"/>
+      <c r="D54" s="77"/>
+      <c r="E54" s="77"/>
       <c r="F54" s="37">
         <f>SUM(F50:F53,F47:F48,F43:F45,F38:F41,F28:F36,F22:F26,F18:F20,F14:F16,F7:F11)</f>
         <v>0</v>
       </c>
       <c r="G54" s="37">
         <f>SUM(G50:G53,G47:G48,G43:G45,G38:G41,G28:G36,G22:G26,G18:G20,G14:G16,G7:G11)</f>
-        <v>-50</v>
+        <v>-53</v>
       </c>
       <c r="H54" s="37">
         <f>SUM(H50:H53,H47:H48,H43:H45,H38:H41,H28:H36,H22:H26,H18:H20,H14:H16,H7:H11)</f>
-        <v>-100</v>
+        <v>-106</v>
       </c>
       <c r="I54" s="38"/>
     </row>
     <row r="55" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="56" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="67" t="s">
+      <c r="A56" s="86" t="s">
         <v>25</v>
       </c>
-      <c r="B56" s="57"/>
-      <c r="C56" s="72" t="s">
+      <c r="B56" s="71"/>
+      <c r="C56" s="70" t="s">
         <v>75</v>
       </c>
-      <c r="D56" s="57"/>
-      <c r="E56" s="57"/>
-      <c r="F56" s="57"/>
-      <c r="G56" s="57"/>
-      <c r="H56" s="57"/>
-      <c r="I56" s="57"/>
+      <c r="D56" s="71"/>
+      <c r="E56" s="71"/>
+      <c r="F56" s="71"/>
+      <c r="G56" s="71"/>
+      <c r="H56" s="71"/>
+      <c r="I56" s="71"/>
     </row>
     <row r="57" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="56" t="s">
+      <c r="A57" s="84" t="s">
         <v>26</v>
       </c>
-      <c r="B57" s="57"/>
-      <c r="C57" s="58" t="s">
+      <c r="B57" s="71"/>
+      <c r="C57" s="85" t="s">
         <v>27</v>
       </c>
-      <c r="D57" s="57"/>
-      <c r="E57" s="57"/>
-      <c r="F57" s="57"/>
-      <c r="G57" s="57"/>
-      <c r="H57" s="57"/>
-      <c r="I57" s="57"/>
+      <c r="D57" s="71"/>
+      <c r="E57" s="71"/>
+      <c r="F57" s="71"/>
+      <c r="G57" s="71"/>
+      <c r="H57" s="71"/>
+      <c r="I57" s="71"/>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A58" s="64" t="s">
+      <c r="A58" s="81" t="s">
         <v>28</v>
       </c>
-      <c r="B58" s="57"/>
-      <c r="C58" s="65" t="s">
+      <c r="B58" s="71"/>
+      <c r="C58" s="82" t="s">
         <v>53</v>
       </c>
-      <c r="D58" s="57"/>
-      <c r="E58" s="57"/>
-      <c r="F58" s="57"/>
-      <c r="G58" s="57"/>
-      <c r="H58" s="57"/>
-      <c r="I58" s="57"/>
+      <c r="D58" s="71"/>
+      <c r="E58" s="71"/>
+      <c r="F58" s="71"/>
+      <c r="G58" s="71"/>
+      <c r="H58" s="71"/>
+      <c r="I58" s="71"/>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A59" s="64" t="s">
+      <c r="A59" s="81" t="s">
         <v>110</v>
       </c>
-      <c r="B59" s="57"/>
-      <c r="C59" s="65" t="s">
+      <c r="B59" s="71"/>
+      <c r="C59" s="82" t="s">
         <v>111</v>
       </c>
-      <c r="D59" s="57"/>
-      <c r="E59" s="57"/>
-      <c r="F59" s="57"/>
-      <c r="G59" s="57"/>
-      <c r="H59" s="57"/>
-      <c r="I59" s="57"/>
+      <c r="D59" s="71"/>
+      <c r="E59" s="71"/>
+      <c r="F59" s="71"/>
+      <c r="G59" s="71"/>
+      <c r="H59" s="71"/>
+      <c r="I59" s="71"/>
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="A17:I17"/>
-    <mergeCell ref="A3:F3"/>
-    <mergeCell ref="A2:I2"/>
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="G3:I3"/>
-    <mergeCell ref="A13:I13"/>
-    <mergeCell ref="A4:F4"/>
-    <mergeCell ref="G4:I4"/>
-    <mergeCell ref="C56:I56"/>
-    <mergeCell ref="A37:I37"/>
-    <mergeCell ref="A46:I46"/>
-    <mergeCell ref="A54:E54"/>
-    <mergeCell ref="A27:I27"/>
-    <mergeCell ref="A6:D6"/>
     <mergeCell ref="A59:B59"/>
     <mergeCell ref="C59:I59"/>
     <mergeCell ref="C58:I58"/>
@@ -3113,6 +3099,20 @@
     <mergeCell ref="A49:I49"/>
     <mergeCell ref="A42:I42"/>
     <mergeCell ref="A21:I21"/>
+    <mergeCell ref="C56:I56"/>
+    <mergeCell ref="A37:I37"/>
+    <mergeCell ref="A46:I46"/>
+    <mergeCell ref="A54:E54"/>
+    <mergeCell ref="A27:I27"/>
+    <mergeCell ref="A17:I17"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="G3:I3"/>
+    <mergeCell ref="A13:I13"/>
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="G4:I4"/>
+    <mergeCell ref="A6:D6"/>
   </mergeCells>
   <phoneticPr fontId="17" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
